--- a/data/dw_table.xlsx
+++ b/data/dw_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B736A13-7FA0-034D-8218-7AAC1F6EBAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AABAFD1-AF11-CC4B-A46D-B0DF1E4C7C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="7940" windowWidth="28800" windowHeight="8660" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
+    <workbookView xWindow="28960" yWindow="-2940" windowWidth="38080" windowHeight="20780" xr2:uid="{E9F1DA6A-4FAA-5143-B6A8-F5EB0E9CBCC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -490,13 +490,13 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>6.8895146412577088E-2</v>
+        <v>6.8895140194388929E-2</v>
       </c>
       <c r="C3">
-        <v>5.2608280646638535E-2</v>
+        <v>5.2608283864960845E-2</v>
       </c>
       <c r="D3">
-        <v>8.7937005811260793E-2</v>
+        <v>8.7937000258794085E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -504,69 +504,69 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>8.9368477539454663E-2</v>
+        <v>8.936848098458243E-2</v>
       </c>
       <c r="C4">
-        <v>7.1361693094938311E-2</v>
+        <v>7.1361688678751381E-2</v>
       </c>
       <c r="D4">
-        <v>0.1039047586920917</v>
+        <v>0.10390475683698316</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>6.5090841675777597E-2</v>
+        <v>8.1982124472113616E-2</v>
       </c>
       <c r="C5">
-        <v>5.1087502395413965E-2</v>
+        <v>6.8952602813391717E-2</v>
       </c>
       <c r="D5">
-        <v>7.9345105734142371E-2</v>
+        <v>9.0994235037606425E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>5.5841162763935519E-2</v>
+        <v>6.5145311673774173E-2</v>
       </c>
       <c r="C6">
-        <v>4.4179170194543448E-2</v>
+        <v>5.095486763796598E-2</v>
       </c>
       <c r="D6">
-        <v>6.4480320921935189E-2</v>
+        <v>7.7995329377991876E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>6.8950211774975873E-2</v>
+        <v>0.20740206225787142</v>
       </c>
       <c r="C7">
-        <v>5.1312027011335852E-2</v>
+        <v>0.16696803248000799</v>
       </c>
       <c r="D7">
-        <v>8.7540296396625333E-2</v>
+        <v>0.23508532548101846</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>0.20722720143266157</v>
+        <v>6.9006130543502436E-2</v>
       </c>
       <c r="C8">
-        <v>0.16617673188559229</v>
+        <v>5.1640700015119112E-2</v>
       </c>
       <c r="D8">
-        <v>0.2360096614537957</v>
+        <v>8.7400660652902085E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -574,13 +574,13 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.16934200918895112</v>
+        <v>0.19900897546278773</v>
       </c>
       <c r="C9">
-        <v>0.10475464189657885</v>
+        <v>0.15529532268025878</v>
       </c>
       <c r="D9">
-        <v>0.25876628163526788</v>
+        <v>0.24658903496730383</v>
       </c>
     </row>
   </sheetData>
